--- a/data/Complete_dataset.xlsx
+++ b/data/Complete_dataset.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alvar\Repository\Roman-Chebba-agriculture\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pc\OneDrive\Documents\repos\Roman-Chebba-agriculture\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3FF4FABD-67CF-4EAA-BE9A-5063829CF196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{939CCA6E-F670-479E-9CBB-F78C59BC8A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Legend" sheetId="1" r:id="rId1"/>
@@ -18,24 +18,11 @@
     <sheet name="Other sites" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1569" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1569" uniqueCount="379">
   <si>
     <t>FID</t>
   </si>
@@ -1169,6 +1156,9 @@
   </si>
   <si>
     <t>Y (32S WGS84)</t>
+  </si>
+  <si>
+    <t>Aquifer_productivity</t>
   </si>
 </sst>
 </file>
@@ -1690,20 +1680,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="53.3984375" customWidth="1"/>
-    <col min="2" max="2" width="78.73046875" customWidth="1"/>
-    <col min="3" max="3" width="52.73046875" customWidth="1"/>
+    <col min="1" max="1" width="53.42578125" customWidth="1"/>
+    <col min="2" max="2" width="78.7109375" customWidth="1"/>
+    <col min="3" max="3" width="52.7109375" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="19.73046875" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="10" width="18" customWidth="1"/>
     <col min="11" max="11" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="34.15" x14ac:dyDescent="1.05">
+    <row r="1" spans="1:11" ht="34.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="20" t="s">
         <v>206</v>
       </c>
@@ -1711,7 +1701,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1719,7 +1709,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1727,7 +1717,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="30.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
         <v>10</v>
       </c>
@@ -1735,7 +1725,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
         <v>181</v>
       </c>
@@ -1743,7 +1733,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>182</v>
       </c>
@@ -1751,7 +1741,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>13</v>
       </c>
@@ -1759,12 +1749,12 @@
         <v>187</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="68.25" x14ac:dyDescent="1.05">
+    <row r="10" spans="1:11" ht="69" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="18" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>123</v>
       </c>
@@ -1796,7 +1786,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -1828,7 +1818,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>68</v>
       </c>
@@ -1860,7 +1850,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -1892,7 +1882,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -1924,7 +1914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -1944,7 +1934,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>66</v>
       </c>
@@ -1964,7 +1954,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>80</v>
       </c>
@@ -1984,7 +1974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -2004,7 +1994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
         <v>202</v>
       </c>
@@ -2018,7 +2008,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>203</v>
       </c>
@@ -2032,7 +2022,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
         <v>204</v>
       </c>
@@ -2046,12 +2036,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>162</v>
       </c>
@@ -2059,7 +2049,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>127</v>
       </c>
@@ -2067,7 +2057,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>128</v>
       </c>
@@ -2075,7 +2065,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>166</v>
       </c>
@@ -2083,7 +2073,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>168</v>
       </c>
@@ -2091,7 +2081,7 @@
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>15</v>
       </c>
@@ -2113,33 +2103,30 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AA93"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.3984375" style="16"/>
-    <col min="2" max="3" width="11.3984375" style="2"/>
-    <col min="4" max="5" width="43.73046875" customWidth="1"/>
-    <col min="6" max="6" width="35.1328125" customWidth="1"/>
-    <col min="7" max="8" width="11.3984375" style="15"/>
-    <col min="9" max="9" width="11.3984375" style="10"/>
-    <col min="10" max="11" width="11.3984375"/>
-    <col min="12" max="12" width="11.3984375" style="11"/>
-    <col min="13" max="13" width="11.3984375" style="10"/>
-    <col min="14" max="14" width="11.3984375"/>
-    <col min="15" max="15" width="14.86328125" customWidth="1"/>
-    <col min="16" max="16" width="11.3984375" style="11"/>
-    <col min="17" max="17" width="11.3984375" style="10"/>
-    <col min="18" max="18" width="11.3984375"/>
+    <col min="1" max="1" width="11.42578125" style="16"/>
+    <col min="2" max="3" width="11.42578125" style="2"/>
+    <col min="4" max="5" width="43.7109375" customWidth="1"/>
+    <col min="6" max="6" width="35.140625" customWidth="1"/>
+    <col min="7" max="8" width="11.42578125" style="15"/>
+    <col min="9" max="9" width="11.42578125" style="10"/>
+    <col min="12" max="12" width="11.42578125" style="11"/>
+    <col min="13" max="13" width="11.42578125" style="10"/>
+    <col min="15" max="15" width="14.85546875" customWidth="1"/>
+    <col min="16" max="16" width="11.42578125" style="11"/>
+    <col min="17" max="17" width="11.42578125" style="10"/>
     <col min="19" max="19" width="18" customWidth="1"/>
-    <col min="20" max="20" width="20.265625" customWidth="1"/>
-    <col min="21" max="21" width="41.265625" customWidth="1"/>
+    <col min="20" max="20" width="20.28515625" customWidth="1"/>
+    <col min="21" max="21" width="41.28515625" customWidth="1"/>
     <col min="22" max="22" width="38" customWidth="1"/>
-    <col min="23" max="23" width="11.3984375" style="11"/>
-    <col min="24" max="24" width="18.1328125" style="10" customWidth="1"/>
+    <col min="23" max="23" width="11.42578125" style="11"/>
+    <col min="24" max="24" width="18.140625" style="10" customWidth="1"/>
     <col min="25" max="25" width="19" customWidth="1"/>
-    <col min="26" max="26" width="25.59765625" style="11" customWidth="1"/>
+    <col min="26" max="26" width="25.5703125" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="28.9" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:27" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
         <v>207</v>
       </c>
@@ -2222,7 +2209,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="26" t="s">
         <v>322</v>
       </c>
@@ -2304,7 +2291,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
         <v>265</v>
       </c>
@@ -2385,7 +2372,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
         <v>267</v>
       </c>
@@ -2469,7 +2456,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="26" t="s">
         <v>344</v>
       </c>
@@ -2553,7 +2540,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="26" t="s">
         <v>268</v>
       </c>
@@ -2635,7 +2622,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
         <v>296</v>
       </c>
@@ -2716,7 +2703,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="26" t="s">
         <v>321</v>
       </c>
@@ -2798,7 +2785,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="26" t="s">
         <v>319</v>
       </c>
@@ -2879,7 +2866,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="26" t="s">
         <v>298</v>
       </c>
@@ -2961,7 +2948,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="26" t="s">
         <v>317</v>
       </c>
@@ -3042,7 +3029,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="26" t="s">
         <v>274</v>
       </c>
@@ -3124,7 +3111,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="26" t="s">
         <v>272</v>
       </c>
@@ -3205,7 +3192,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="26" t="s">
         <v>261</v>
       </c>
@@ -3287,7 +3274,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="26" t="s">
         <v>260</v>
       </c>
@@ -3369,7 +3356,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="26" t="s">
         <v>262</v>
       </c>
@@ -3451,7 +3438,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
         <v>263</v>
       </c>
@@ -3532,7 +3519,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" s="26" t="s">
         <v>270</v>
       </c>
@@ -3616,7 +3603,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" s="26" t="s">
         <v>276</v>
       </c>
@@ -3696,7 +3683,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" s="26" t="s">
         <v>278</v>
       </c>
@@ -3776,7 +3763,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" s="26" t="s">
         <v>286</v>
       </c>
@@ -3860,7 +3847,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" s="26" t="s">
         <v>288</v>
       </c>
@@ -3944,7 +3931,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" s="26" t="s">
         <v>290</v>
       </c>
@@ -4025,7 +4012,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" s="26" t="s">
         <v>284</v>
       </c>
@@ -4106,7 +4093,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" s="26" t="s">
         <v>282</v>
       </c>
@@ -4187,7 +4174,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" s="26" t="s">
         <v>280</v>
       </c>
@@ -4268,7 +4255,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" s="26" t="s">
         <v>257</v>
       </c>
@@ -4349,7 +4336,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28" s="26" t="s">
         <v>259</v>
       </c>
@@ -4430,7 +4417,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29" s="26" t="s">
         <v>255</v>
       </c>
@@ -4513,7 +4500,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A30" s="26" t="s">
         <v>315</v>
       </c>
@@ -4595,7 +4582,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A31" s="26" t="s">
         <v>254</v>
       </c>
@@ -4675,7 +4662,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32" s="26" t="s">
         <v>251</v>
       </c>
@@ -4756,7 +4743,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33" s="26" t="s">
         <v>249</v>
       </c>
@@ -4838,7 +4825,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A34" s="26" t="s">
         <v>253</v>
       </c>
@@ -4918,7 +4905,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A35" s="26" t="s">
         <v>247</v>
       </c>
@@ -5000,7 +4987,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A36" s="26" t="s">
         <v>246</v>
       </c>
@@ -5082,7 +5069,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A37" s="26" t="s">
         <v>245</v>
       </c>
@@ -5164,7 +5151,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A38" s="26" t="s">
         <v>243</v>
       </c>
@@ -5248,7 +5235,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A39" s="26" t="s">
         <v>350</v>
       </c>
@@ -5332,7 +5319,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A40" s="26" t="s">
         <v>241</v>
       </c>
@@ -5413,7 +5400,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A41" s="26" t="s">
         <v>240</v>
       </c>
@@ -5495,7 +5482,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A42" s="26" t="s">
         <v>213</v>
       </c>
@@ -5579,7 +5566,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A43" s="26" t="s">
         <v>214</v>
       </c>
@@ -5661,7 +5648,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A44" s="26" t="s">
         <v>211</v>
       </c>
@@ -5743,7 +5730,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A45" s="26" t="s">
         <v>210</v>
       </c>
@@ -5825,7 +5812,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A46" s="26" t="s">
         <v>209</v>
       </c>
@@ -5907,7 +5894,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A47" s="26" t="s">
         <v>208</v>
       </c>
@@ -5989,7 +5976,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A48" s="26" t="s">
         <v>216</v>
       </c>
@@ -6073,7 +6060,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A49" s="26" t="s">
         <v>215</v>
       </c>
@@ -6155,7 +6142,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A50" s="26" t="s">
         <v>239</v>
       </c>
@@ -6237,7 +6224,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A51" s="26" t="s">
         <v>237</v>
       </c>
@@ -6319,7 +6306,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A52" s="26" t="s">
         <v>236</v>
       </c>
@@ -6403,7 +6390,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A53" s="26" t="s">
         <v>353</v>
       </c>
@@ -6487,7 +6474,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A54" s="26" t="s">
         <v>235</v>
       </c>
@@ -6571,7 +6558,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A55" s="26" t="s">
         <v>232</v>
       </c>
@@ -6655,7 +6642,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A56" s="26" t="s">
         <v>233</v>
       </c>
@@ -6737,7 +6724,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A57" s="26" t="s">
         <v>234</v>
       </c>
@@ -6819,7 +6806,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A58" s="26" t="s">
         <v>226</v>
       </c>
@@ -6900,7 +6887,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A59" s="26" t="s">
         <v>228</v>
       </c>
@@ -6984,7 +6971,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A60" s="26" t="s">
         <v>313</v>
       </c>
@@ -7066,7 +7053,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A61" s="26" t="s">
         <v>292</v>
       </c>
@@ -7146,7 +7133,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A62" s="26" t="s">
         <v>293</v>
       </c>
@@ -7228,7 +7215,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A63" s="26" t="s">
         <v>307</v>
       </c>
@@ -7310,7 +7297,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A64" s="26" t="s">
         <v>305</v>
       </c>
@@ -7392,7 +7379,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A65" s="26" t="s">
         <v>309</v>
       </c>
@@ -7476,7 +7463,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A66" s="26" t="s">
         <v>326</v>
       </c>
@@ -7557,7 +7544,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A67" s="26" t="s">
         <v>306</v>
       </c>
@@ -7639,7 +7626,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="68" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A68" s="26" t="s">
         <v>303</v>
       </c>
@@ -7721,7 +7708,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A69" s="26" t="s">
         <v>301</v>
       </c>
@@ -7803,7 +7790,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A70" s="26" t="s">
         <v>300</v>
       </c>
@@ -7887,7 +7874,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="71" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A71" s="26" t="s">
         <v>304</v>
       </c>
@@ -7969,7 +7956,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A72" s="26" t="s">
         <v>325</v>
       </c>
@@ -8053,7 +8040,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A73" s="26" t="s">
         <v>323</v>
       </c>
@@ -8137,7 +8124,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="74" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A74" s="26" t="s">
         <v>330</v>
       </c>
@@ -8219,7 +8206,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="75" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A75" s="26" t="s">
         <v>334</v>
       </c>
@@ -8301,7 +8288,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A76" s="26" t="s">
         <v>332</v>
       </c>
@@ -8385,7 +8372,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A77" s="26" t="s">
         <v>328</v>
       </c>
@@ -8466,7 +8453,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="78" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A78" s="16" t="s">
         <v>336</v>
       </c>
@@ -8550,7 +8537,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A79" s="16" t="s">
         <v>338</v>
       </c>
@@ -8631,7 +8618,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A80" s="16" t="s">
         <v>340</v>
       </c>
@@ -8712,7 +8699,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A81" s="16" t="s">
         <v>224</v>
       </c>
@@ -8793,7 +8780,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A82" s="16" t="s">
         <v>358</v>
       </c>
@@ -8874,7 +8861,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A83" s="16" t="s">
         <v>223</v>
       </c>
@@ -8958,7 +8945,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A84" s="16" t="s">
         <v>312</v>
       </c>
@@ -9039,7 +9026,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="85" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A85" s="16" t="s">
         <v>220</v>
       </c>
@@ -9120,7 +9107,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A86" s="16" t="s">
         <v>222</v>
       </c>
@@ -9202,7 +9189,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="87" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A87" s="16" t="s">
         <v>219</v>
       </c>
@@ -9286,7 +9273,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="88" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A88" s="16" t="s">
         <v>229</v>
       </c>
@@ -9368,7 +9355,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A89" s="16" t="s">
         <v>230</v>
       </c>
@@ -9450,7 +9437,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A90" s="16" t="s">
         <v>231</v>
       </c>
@@ -9532,7 +9519,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="91" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A91" s="16" t="s">
         <v>311</v>
       </c>
@@ -9614,7 +9601,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A92" s="16" t="s">
         <v>368</v>
       </c>
@@ -9696,7 +9683,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="93" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A93" s="16" t="s">
         <v>217</v>
       </c>
@@ -9789,27 +9776,27 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AE53"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="34.1328125" customWidth="1"/>
-    <col min="4" max="4" width="16.265625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="14.86328125" style="2" customWidth="1"/>
-    <col min="9" max="14" width="11.3984375" style="15"/>
-    <col min="15" max="15" width="11.3984375" style="10"/>
+    <col min="3" max="3" width="34.140625" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="2" customWidth="1"/>
+    <col min="9" max="14" width="11.42578125" style="15"/>
+    <col min="15" max="15" width="11.42578125" style="10"/>
     <col min="16" max="16" width="16" customWidth="1"/>
     <col min="17" max="17" width="18" customWidth="1"/>
     <col min="18" max="18" width="12" style="11" customWidth="1"/>
-    <col min="19" max="19" width="11.3984375" style="10"/>
+    <col min="19" max="19" width="11.42578125" style="10"/>
     <col min="21" max="21" width="20" customWidth="1"/>
     <col min="22" max="22" width="14" customWidth="1"/>
     <col min="23" max="23" width="26" customWidth="1"/>
     <col min="24" max="24" width="16" customWidth="1"/>
     <col min="25" max="25" width="12" style="11" customWidth="1"/>
-    <col min="26" max="26" width="29.3984375" style="10" customWidth="1"/>
+    <col min="26" max="26" width="29.42578125" style="10" customWidth="1"/>
     <col min="28" max="28" width="21" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="5" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:29" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -9892,13 +9879,13 @@
         <v>190</v>
       </c>
       <c r="AB1" s="23" t="s">
-        <v>196</v>
+        <v>378</v>
       </c>
       <c r="AC1" s="5" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>7</v>
       </c>
@@ -9995,7 +9982,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>8</v>
       </c>
@@ -10092,7 +10079,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9</v>
       </c>
@@ -10189,7 +10176,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>10</v>
       </c>
@@ -10286,7 +10273,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>11</v>
       </c>
@@ -10383,7 +10370,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>12</v>
       </c>
@@ -10480,7 +10467,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>19</v>
       </c>
@@ -10577,7 +10564,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>20</v>
       </c>
@@ -10674,7 +10661,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>21</v>
       </c>
@@ -10771,7 +10758,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>22</v>
       </c>
@@ -10868,7 +10855,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>23</v>
       </c>
@@ -10965,7 +10952,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>24</v>
       </c>
@@ -11062,7 +11049,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>25</v>
       </c>
@@ -11159,7 +11146,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>26</v>
       </c>
@@ -11256,7 +11243,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>32</v>
       </c>
@@ -11353,7 +11340,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>33</v>
       </c>
@@ -11450,7 +11437,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="18" spans="1:31" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>34</v>
       </c>
@@ -11547,7 +11534,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="19" spans="1:31" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>35</v>
       </c>
@@ -11645,7 +11632,7 @@
       </c>
       <c r="AE19" s="13"/>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>36</v>
       </c>
@@ -11742,7 +11729,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>44</v>
       </c>
@@ -11839,7 +11826,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>45</v>
       </c>
@@ -11936,7 +11923,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>46</v>
       </c>
@@ -12033,7 +12020,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>47</v>
       </c>
@@ -12130,7 +12117,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>48</v>
       </c>
@@ -12227,7 +12214,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>49</v>
       </c>
@@ -12324,7 +12311,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>50</v>
       </c>
@@ -12421,7 +12408,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>51</v>
       </c>
@@ -12518,7 +12505,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="29" spans="1:31" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:31" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="35">
         <v>0</v>
       </c>
@@ -12615,7 +12602,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="30" spans="1:31" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:31" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="35">
         <v>1</v>
       </c>
@@ -12712,7 +12699,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:31" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:31" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="35">
         <v>2</v>
       </c>
@@ -12809,7 +12796,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:31" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:31" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="35">
         <v>3</v>
       </c>
@@ -12906,7 +12893,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="35">
         <v>4</v>
       </c>
@@ -13003,7 +12990,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="34" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="35">
         <v>5</v>
       </c>
@@ -13100,7 +13087,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="35">
         <v>6</v>
       </c>
@@ -13197,7 +13184,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="36" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="35">
         <v>13</v>
       </c>
@@ -13294,7 +13281,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="37" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="35">
         <v>14</v>
       </c>
@@ -13391,7 +13378,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="38" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="35">
         <v>15</v>
       </c>
@@ -13488,7 +13475,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="39" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="35">
         <v>16</v>
       </c>
@@ -13585,7 +13572,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="40" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="35">
         <v>17</v>
       </c>
@@ -13682,7 +13669,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="41" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="35">
         <v>18</v>
       </c>
@@ -13779,7 +13766,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="42" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="35">
         <v>27</v>
       </c>
@@ -13876,7 +13863,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="43" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="35">
         <v>28</v>
       </c>
@@ -13973,7 +13960,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="44" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="35">
         <v>29</v>
       </c>
@@ -14070,7 +14057,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="45" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="35">
         <v>30</v>
       </c>
@@ -14167,7 +14154,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="46" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="35">
         <v>31</v>
       </c>
@@ -14264,7 +14251,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="47" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="35">
         <v>37</v>
       </c>
@@ -14361,7 +14348,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="48" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="35">
         <v>38</v>
       </c>
@@ -14458,7 +14445,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="49" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="35">
         <v>39</v>
       </c>
@@ -14555,7 +14542,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="50" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="35">
         <v>40</v>
       </c>
@@ -14652,7 +14639,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="51" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="35">
         <v>41</v>
       </c>
@@ -14749,7 +14736,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="52" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="35">
         <v>42</v>
       </c>
@@ -14846,7 +14833,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="53" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="35">
         <v>43</v>
       </c>

--- a/data/Complete_dataset.xlsx
+++ b/data/Complete_dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alvar\Repository\Roman-Chebba-agriculture\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ECB0807-6E4E-43CD-9544-621EA55593DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF6732F3-8DFF-4066-A081-E92AE62B92A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1570" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1570" uniqueCount="379">
   <si>
     <t>FID</t>
   </si>
@@ -623,9 +623,6 @@
   </si>
   <si>
     <t>CSIF-M</t>
-  </si>
-  <si>
-    <t>Aquifer producitivity</t>
   </si>
   <si>
     <t>Unconsolidated sedimentary aquifer</t>
@@ -1707,7 +1704,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="34.15" x14ac:dyDescent="1.05">
       <c r="A1" s="20" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B1" s="19" t="s">
         <v>180</v>
@@ -2008,13 +2005,13 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A20" s="16" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C20" s="24" t="s">
+        <v>196</v>
+      </c>
+      <c r="E20" s="16" t="s">
         <v>197</v>
-      </c>
-      <c r="E20" s="16" t="s">
-        <v>198</v>
       </c>
       <c r="F20">
         <v>4</v>
@@ -2022,13 +2019,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A21" s="16" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C21" t="s">
+        <v>198</v>
+      </c>
+      <c r="E21" s="16" t="s">
         <v>199</v>
-      </c>
-      <c r="E21" s="16" t="s">
-        <v>200</v>
       </c>
       <c r="F21">
         <v>3</v>
@@ -2036,13 +2033,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A22" s="16" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C22" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -2050,7 +2047,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A23" s="16" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.45">
@@ -2140,25 +2137,25 @@
   <sheetData>
     <row r="1" spans="1:28" ht="28.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="33" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B1" s="34" t="s">
+        <v>375</v>
+      </c>
+      <c r="C1" s="34" t="s">
         <v>376</v>
-      </c>
-      <c r="C1" s="34" t="s">
-        <v>377</v>
       </c>
       <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="33" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F1" s="33" t="s">
         <v>6</v>
       </c>
       <c r="G1" s="33" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1" s="14" t="s">
         <v>8</v>
@@ -2218,15 +2215,15 @@
         <v>190</v>
       </c>
       <c r="AA1" s="23" t="s">
-        <v>196</v>
+        <v>377</v>
       </c>
       <c r="AB1" s="5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A2" s="26" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B2" s="28">
         <v>673557</v>
@@ -2309,7 +2306,7 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A3" s="26" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B3" s="28">
         <v>671700</v>
@@ -2318,7 +2315,7 @@
         <v>3911030</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G3" s="16" t="s">
         <v>72</v>
@@ -2390,7 +2387,7 @@
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A4" s="26" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B4" s="28">
         <v>671818</v>
@@ -2399,13 +2396,13 @@
         <v>3909099</v>
       </c>
       <c r="D4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H4" s="15">
         <v>1142.6097649999999</v>
@@ -2474,7 +2471,7 @@
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A5" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B5" s="28">
         <v>671991</v>
@@ -2483,13 +2480,13 @@
         <v>3907999</v>
       </c>
       <c r="D5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H5" s="15">
         <v>72.562110000000004</v>
@@ -2558,7 +2555,7 @@
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A6" s="26" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B6" s="28">
         <v>671599</v>
@@ -2567,7 +2564,7 @@
         <v>3906697</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="25"/>
@@ -2641,7 +2638,7 @@
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A7" s="26" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B7" s="28">
         <v>670861</v>
@@ -2650,7 +2647,7 @@
         <v>3905556</v>
       </c>
       <c r="D7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G7" s="16" t="s">
         <v>72</v>
@@ -2722,7 +2719,7 @@
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A8" s="26" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B8" s="28">
         <v>672158</v>
@@ -2805,7 +2802,7 @@
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A9" s="26" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B9" s="28">
         <v>672714</v>
@@ -2814,7 +2811,7 @@
         <v>3905546</v>
       </c>
       <c r="D9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G9" s="16" t="s">
         <v>72</v>
@@ -2886,7 +2883,7 @@
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A10" s="26" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B10" s="28">
         <v>675371</v>
@@ -2895,7 +2892,7 @@
         <v>3904906</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E10" s="25"/>
       <c r="F10" s="25"/>
@@ -2969,7 +2966,7 @@
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A11" s="26" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B11" s="28">
         <v>674256</v>
@@ -2978,7 +2975,7 @@
         <v>3906143</v>
       </c>
       <c r="D11" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G11" s="16" t="s">
         <v>72</v>
@@ -3050,7 +3047,7 @@
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A12" s="26" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B12" s="28">
         <v>674496</v>
@@ -3059,7 +3056,7 @@
         <v>3908159</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E12" s="25"/>
       <c r="F12" s="25"/>
@@ -3133,7 +3130,7 @@
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A13" s="26" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B13" s="28">
         <v>673456</v>
@@ -3142,7 +3139,7 @@
         <v>3908909</v>
       </c>
       <c r="D13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G13" s="16" t="s">
         <v>72</v>
@@ -3214,7 +3211,7 @@
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A14" s="26" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B14" s="28">
         <v>674155</v>
@@ -3228,7 +3225,7 @@
       <c r="E14" s="27"/>
       <c r="F14" s="27"/>
       <c r="G14" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H14" s="15">
         <v>616.61077299999999</v>
@@ -3297,7 +3294,7 @@
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A15" s="26" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B15" s="28">
         <v>674747</v>
@@ -3311,7 +3308,7 @@
       <c r="E15" s="27"/>
       <c r="F15" s="27"/>
       <c r="G15" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H15" s="15">
         <v>222.07216099999999</v>
@@ -3380,7 +3377,7 @@
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A16" s="26" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B16" s="28">
         <v>673800</v>
@@ -3463,7 +3460,7 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A17" s="26" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B17" s="28">
         <v>674483</v>
@@ -3472,7 +3469,7 @@
         <v>3911483</v>
       </c>
       <c r="D17" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G17" s="16" t="s">
         <v>72</v>
@@ -3544,7 +3541,7 @@
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A18" s="26" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B18" s="28">
         <v>677105</v>
@@ -3553,13 +3550,13 @@
         <v>3910330</v>
       </c>
       <c r="D18" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E18">
         <v>1</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H18" s="15">
         <v>187.952427</v>
@@ -3628,7 +3625,7 @@
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A19" s="26" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B19" s="28">
         <v>678188</v>
@@ -3637,7 +3634,7 @@
         <v>3908273</v>
       </c>
       <c r="D19" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G19" s="16" t="s">
         <v>72</v>
@@ -3708,7 +3705,7 @@
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A20" s="26" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B20" s="28">
         <v>676926</v>
@@ -3717,7 +3714,7 @@
         <v>3907006</v>
       </c>
       <c r="D20" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G20" s="16" t="s">
         <v>72</v>
@@ -3788,7 +3785,7 @@
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A21" s="26" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B21" s="28">
         <v>677896</v>
@@ -3797,13 +3794,13 @@
         <v>3905538</v>
       </c>
       <c r="D21" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E21">
         <v>0</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H21" s="15">
         <v>109.52525300000001</v>
@@ -3872,7 +3869,7 @@
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A22" s="26" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B22" s="28">
         <v>678152</v>
@@ -3881,13 +3878,13 @@
         <v>3904749</v>
       </c>
       <c r="D22" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E22">
         <v>0</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H22" s="15">
         <v>136.43447499999999</v>
@@ -3956,7 +3953,7 @@
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A23" s="26" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B23" s="28">
         <v>680243</v>
@@ -3965,7 +3962,7 @@
         <v>3904463</v>
       </c>
       <c r="D23" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G23" s="16" t="s">
         <v>72</v>
@@ -4037,7 +4034,7 @@
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A24" s="26" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B24" s="28">
         <v>678950</v>
@@ -4046,7 +4043,7 @@
         <v>3905598</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G24" s="16" t="s">
         <v>72</v>
@@ -4118,7 +4115,7 @@
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A25" s="26" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B25" s="28">
         <v>681269</v>
@@ -4127,7 +4124,7 @@
         <v>3906610</v>
       </c>
       <c r="D25" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G25" s="16" t="s">
         <v>72</v>
@@ -4199,7 +4196,7 @@
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A26" s="26" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B26" s="28">
         <v>680882</v>
@@ -4208,7 +4205,7 @@
         <v>3907666</v>
       </c>
       <c r="D26" s="25" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E26" s="25"/>
       <c r="F26" s="25"/>
@@ -4281,7 +4278,7 @@
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A27" s="26" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B27" s="28">
         <v>679303</v>
@@ -4290,7 +4287,7 @@
         <v>3911494</v>
       </c>
       <c r="D27" s="25" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E27" s="25"/>
       <c r="F27" s="25"/>
@@ -4363,7 +4360,7 @@
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A28" s="26" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B28" s="28">
         <v>682499</v>
@@ -4445,7 +4442,7 @@
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A29" s="26" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B29" s="28">
         <v>681692</v>
@@ -4454,7 +4451,7 @@
         <v>3909689</v>
       </c>
       <c r="D29" s="25" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E29" s="25">
         <v>1</v>
@@ -4463,7 +4460,7 @@
         <v>1</v>
       </c>
       <c r="G29" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H29" s="15">
         <v>193.14150699999999</v>
@@ -4531,7 +4528,7 @@
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A30" s="26" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B30" s="28">
         <v>682690</v>
@@ -4540,7 +4537,7 @@
         <v>3908499</v>
       </c>
       <c r="D30" s="25" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E30" s="25"/>
       <c r="F30" s="25"/>
@@ -4614,7 +4611,7 @@
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A31" s="26" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B31" s="28">
         <v>686298</v>
@@ -4630,7 +4627,7 @@
       </c>
       <c r="F31" s="27"/>
       <c r="G31" s="16" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H31" s="15">
         <v>876.15779099999997</v>
@@ -4663,19 +4660,19 @@
         <v>3</v>
       </c>
       <c r="R31" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="S31" t="s">
         <v>370</v>
       </c>
-      <c r="S31" t="s">
+      <c r="T31" t="s">
+        <v>372</v>
+      </c>
+      <c r="U31" t="s">
         <v>371</v>
       </c>
-      <c r="T31" t="s">
+      <c r="V31" t="s">
         <v>373</v>
-      </c>
-      <c r="U31" t="s">
-        <v>372</v>
-      </c>
-      <c r="V31" t="s">
-        <v>374</v>
       </c>
       <c r="W31" t="s">
         <v>149</v>
@@ -4695,7 +4692,7 @@
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A32" s="26" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B32" s="28">
         <v>684533</v>
@@ -4704,10 +4701,10 @@
         <v>3907350</v>
       </c>
       <c r="D32" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G32" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H32" s="15">
         <v>115.871628</v>
@@ -4776,7 +4773,7 @@
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A33" s="26" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B33" s="28">
         <v>685442</v>
@@ -4785,7 +4782,7 @@
         <v>3907151</v>
       </c>
       <c r="D33" s="25" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E33" s="25"/>
       <c r="F33" s="25"/>
@@ -4859,7 +4856,7 @@
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A34" s="26" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B34" s="28">
         <v>687998</v>
@@ -4868,14 +4865,14 @@
         <v>3907633</v>
       </c>
       <c r="D34" s="25" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E34" s="25">
         <v>1</v>
       </c>
       <c r="F34" s="25"/>
       <c r="G34" s="16" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H34" s="15">
         <v>897.88304300000004</v>
@@ -4908,19 +4905,19 @@
         <v>3</v>
       </c>
       <c r="R34" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="S34" t="s">
         <v>370</v>
       </c>
-      <c r="S34" t="s">
+      <c r="T34" t="s">
+        <v>372</v>
+      </c>
+      <c r="U34" t="s">
         <v>371</v>
       </c>
-      <c r="T34" t="s">
+      <c r="V34" t="s">
         <v>373</v>
-      </c>
-      <c r="U34" t="s">
-        <v>372</v>
-      </c>
-      <c r="V34" t="s">
-        <v>374</v>
       </c>
       <c r="W34" t="s">
         <v>149</v>
@@ -4940,7 +4937,7 @@
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A35" s="26" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B35" s="28">
         <v>686097</v>
@@ -4949,7 +4946,7 @@
         <v>3906587</v>
       </c>
       <c r="D35" s="25" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E35" s="25"/>
       <c r="F35" s="25"/>
@@ -5023,7 +5020,7 @@
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A36" s="26" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B36" s="28">
         <v>685472</v>
@@ -5106,7 +5103,7 @@
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A37" s="26" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B37" s="28">
         <v>687168</v>
@@ -5189,7 +5186,7 @@
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A38" s="26" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B38" s="28">
         <v>687744</v>
@@ -5198,14 +5195,14 @@
         <v>3905102</v>
       </c>
       <c r="D38" s="25" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E38" s="25">
         <v>0</v>
       </c>
       <c r="F38" s="25"/>
       <c r="G38" s="16" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H38" s="15">
         <v>613.19806000000005</v>
@@ -5274,7 +5271,7 @@
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A39" s="26" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B39" s="28">
         <v>686473</v>
@@ -5283,7 +5280,7 @@
         <v>3905027</v>
       </c>
       <c r="D39" s="25" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E39" s="25">
         <v>1</v>
@@ -5292,7 +5289,7 @@
         <v>1</v>
       </c>
       <c r="G39" s="16" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H39" s="15">
         <v>1293.315985</v>
@@ -5361,7 +5358,7 @@
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A40" s="26" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B40" s="28">
         <v>687450</v>
@@ -5370,7 +5367,7 @@
         <v>3903958</v>
       </c>
       <c r="D40" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G40" s="16" t="s">
         <v>72</v>
@@ -5442,7 +5439,7 @@
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A41" s="26" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B41" s="28">
         <v>689650</v>
@@ -5525,7 +5522,7 @@
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A42" s="26" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B42" s="28">
         <v>693174</v>
@@ -5534,13 +5531,13 @@
         <v>3902901</v>
       </c>
       <c r="D42" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E42">
         <v>0</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H42" s="15">
         <v>2066.4997020000001</v>
@@ -5609,7 +5606,7 @@
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A43" s="26" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B43" s="28">
         <v>692634</v>
@@ -5692,7 +5689,7 @@
     </row>
     <row r="44" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A44" s="26" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B44" s="28">
         <v>692999</v>
@@ -5775,7 +5772,7 @@
     </row>
     <row r="45" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A45" s="26" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B45" s="28">
         <v>694012</v>
@@ -5858,7 +5855,7 @@
     </row>
     <row r="46" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A46" s="26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B46" s="28">
         <v>694920</v>
@@ -5941,7 +5938,7 @@
     </row>
     <row r="47" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A47" s="26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B47" s="28">
         <v>694604</v>
@@ -5950,12 +5947,12 @@
         <v>3900197</v>
       </c>
       <c r="D47" s="25" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E47" s="25"/>
       <c r="F47" s="25"/>
       <c r="G47" s="16" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H47" s="15">
         <v>632.11020799999994</v>
@@ -6024,7 +6021,7 @@
     </row>
     <row r="48" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A48" s="26" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B48" s="28">
         <v>691573</v>
@@ -6040,7 +6037,7 @@
       </c>
       <c r="F48" s="27"/>
       <c r="G48" s="16" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H48" s="15">
         <v>585.28026399999999</v>
@@ -6109,7 +6106,7 @@
     </row>
     <row r="49" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A49" s="26" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B49" s="28">
         <v>691246</v>
@@ -6192,7 +6189,7 @@
     </row>
     <row r="50" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A50" s="26" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B50" s="28">
         <v>689505</v>
@@ -6201,7 +6198,7 @@
         <v>3901282</v>
       </c>
       <c r="D50" s="25" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E50" s="25"/>
       <c r="F50" s="25"/>
@@ -6275,7 +6272,7 @@
     </row>
     <row r="51" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A51" s="26" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B51" s="28">
         <v>686145</v>
@@ -6284,7 +6281,7 @@
         <v>3901184</v>
       </c>
       <c r="D51" s="25" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E51" s="25"/>
       <c r="F51" s="25"/>
@@ -6358,7 +6355,7 @@
     </row>
     <row r="52" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A52" s="26" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B52" s="28">
         <v>684298</v>
@@ -6376,7 +6373,7 @@
         <v>1</v>
       </c>
       <c r="G52" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H52" s="15">
         <v>561.35809900000004</v>
@@ -6445,7 +6442,7 @@
     </row>
     <row r="53" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A53" s="26" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B53" s="28">
         <v>684489</v>
@@ -6463,7 +6460,7 @@
         <v>1</v>
       </c>
       <c r="G53" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H53" s="15">
         <v>191.54125199999999</v>
@@ -6532,7 +6529,7 @@
     </row>
     <row r="54" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A54" s="26" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B54" s="28">
         <v>684699</v>
@@ -6548,7 +6545,7 @@
       </c>
       <c r="F54" s="27"/>
       <c r="G54" s="16" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H54" s="15">
         <v>772.075919</v>
@@ -6617,7 +6614,7 @@
     </row>
     <row r="55" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A55" s="26" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B55" s="28">
         <v>684014</v>
@@ -6626,7 +6623,7 @@
         <v>3898977</v>
       </c>
       <c r="D55" s="25" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E55" s="25">
         <v>1</v>
@@ -6635,7 +6632,7 @@
         <v>1</v>
       </c>
       <c r="G55" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H55" s="15">
         <v>115.253652</v>
@@ -6704,7 +6701,7 @@
     </row>
     <row r="56" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A56" s="26" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B56" s="28">
         <v>683648</v>
@@ -6787,7 +6784,7 @@
     </row>
     <row r="57" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A57" s="26" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B57" s="28">
         <v>682570</v>
@@ -6801,7 +6798,7 @@
       <c r="E57" s="27"/>
       <c r="F57" s="27"/>
       <c r="G57" s="16" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H57" s="15">
         <v>236.38143299999999</v>
@@ -6870,7 +6867,7 @@
     </row>
     <row r="58" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A58" s="26" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B58" s="28">
         <v>679696</v>
@@ -6879,10 +6876,10 @@
         <v>3899980</v>
       </c>
       <c r="D58" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G58" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H58" s="15">
         <v>707.23775799999999</v>
@@ -6951,7 +6948,7 @@
     </row>
     <row r="59" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A59" s="26" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B59" s="28">
         <v>680756</v>
@@ -6969,7 +6966,7 @@
         <v>0</v>
       </c>
       <c r="G59" s="16" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H59" s="15">
         <v>560.72416799999996</v>
@@ -7038,7 +7035,7 @@
     </row>
     <row r="60" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A60" s="26" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B60" s="28">
         <v>678315</v>
@@ -7047,14 +7044,14 @@
         <v>3900001</v>
       </c>
       <c r="D60" s="25" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E60" s="25"/>
       <c r="F60" s="25">
         <v>1</v>
       </c>
       <c r="G60" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H60" s="15">
         <v>467.409448</v>
@@ -7123,7 +7120,7 @@
     </row>
     <row r="61" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A61" s="26" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B61" s="28">
         <v>681040</v>
@@ -7204,7 +7201,7 @@
     </row>
     <row r="62" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A62" s="26" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B62" s="28">
         <v>678528</v>
@@ -7213,7 +7210,7 @@
         <v>3902687</v>
       </c>
       <c r="D62" s="25" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E62" s="25"/>
       <c r="F62" s="25"/>
@@ -7287,7 +7284,7 @@
     </row>
     <row r="63" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A63" s="26" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B63" s="28">
         <v>676969</v>
@@ -7296,7 +7293,7 @@
         <v>3900772</v>
       </c>
       <c r="D63" s="25" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E63" s="25"/>
       <c r="F63" s="25"/>
@@ -7370,7 +7367,7 @@
     </row>
     <row r="64" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A64" s="26" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B64" s="28">
         <v>676116</v>
@@ -7453,7 +7450,7 @@
     </row>
     <row r="65" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A65" s="26" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B65" s="28">
         <v>676654</v>
@@ -7462,13 +7459,13 @@
         <v>3900235</v>
       </c>
       <c r="D65" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E65">
         <v>1</v>
       </c>
       <c r="G65" s="16" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H65" s="15">
         <v>199.24893399999999</v>
@@ -7537,7 +7534,7 @@
     </row>
     <row r="66" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A66" s="26" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B66" s="28">
         <v>674092</v>
@@ -7546,7 +7543,7 @@
         <v>3901546</v>
       </c>
       <c r="D66" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G66" s="16" t="s">
         <v>72</v>
@@ -7618,7 +7615,7 @@
     </row>
     <row r="67" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A67" s="26" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B67" s="28">
         <v>677159</v>
@@ -7701,7 +7698,7 @@
     </row>
     <row r="68" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A68" s="26" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B68" s="28">
         <v>675619</v>
@@ -7784,7 +7781,7 @@
     </row>
     <row r="69" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A69" s="26" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B69" s="28">
         <v>674942</v>
@@ -7793,7 +7790,7 @@
         <v>3902800</v>
       </c>
       <c r="D69" s="25" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E69" s="25"/>
       <c r="F69" s="25"/>
@@ -7867,7 +7864,7 @@
     </row>
     <row r="70" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A70" s="26" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B70" s="28">
         <v>672146</v>
@@ -7876,7 +7873,7 @@
         <v>3903604</v>
       </c>
       <c r="D70" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E70">
         <v>1</v>
@@ -7885,7 +7882,7 @@
         <v>1</v>
       </c>
       <c r="G70" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H70" s="15">
         <v>784.59630200000004</v>
@@ -7954,7 +7951,7 @@
     </row>
     <row r="71" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A71" s="26" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B71" s="28">
         <v>671915</v>
@@ -8037,7 +8034,7 @@
     </row>
     <row r="72" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A72" s="26" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B72" s="28">
         <v>668812</v>
@@ -8046,14 +8043,14 @@
         <v>3901697</v>
       </c>
       <c r="D72" s="25" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E72" s="25">
         <v>1</v>
       </c>
       <c r="F72" s="25"/>
       <c r="G72" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H72" s="15">
         <v>305.60256199999998</v>
@@ -8122,7 +8119,7 @@
     </row>
     <row r="73" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A73" s="26" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B73" s="28">
         <v>664249</v>
@@ -8131,7 +8128,7 @@
         <v>3901775</v>
       </c>
       <c r="D73" s="25" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E73" s="25">
         <v>0</v>
@@ -8140,7 +8137,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H73" s="15">
         <v>426.51115499999997</v>
@@ -8209,7 +8206,7 @@
     </row>
     <row r="74" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A74" s="26" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B74" s="28">
         <v>667358</v>
@@ -8218,7 +8215,7 @@
         <v>3897928</v>
       </c>
       <c r="D74" s="25" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E74" s="25"/>
       <c r="F74" s="25"/>
@@ -8292,7 +8289,7 @@
     </row>
     <row r="75" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A75" s="26" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B75" s="28">
         <v>668548</v>
@@ -8301,7 +8298,7 @@
         <v>3892734</v>
       </c>
       <c r="D75" s="25" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E75" s="25"/>
       <c r="F75" s="25"/>
@@ -8375,7 +8372,7 @@
     </row>
     <row r="76" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A76" s="26" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B76" s="28">
         <v>670010</v>
@@ -8384,7 +8381,7 @@
         <v>3894790</v>
       </c>
       <c r="D76" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E76">
         <v>1</v>
@@ -8393,7 +8390,7 @@
         <v>1</v>
       </c>
       <c r="G76" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H76" s="15">
         <v>78.814207999999994</v>
@@ -8462,7 +8459,7 @@
     </row>
     <row r="77" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A77" s="26" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B77" s="28">
         <v>670267</v>
@@ -8471,7 +8468,7 @@
         <v>3896929</v>
       </c>
       <c r="D77" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G77" s="16" t="s">
         <v>72</v>
@@ -8543,7 +8540,7 @@
     </row>
     <row r="78" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A78" s="16" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B78" s="2">
         <v>675010</v>
@@ -8552,7 +8549,7 @@
         <v>3892538</v>
       </c>
       <c r="D78" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E78">
         <v>1</v>
@@ -8561,7 +8558,7 @@
         <v>1</v>
       </c>
       <c r="G78" s="16" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H78" s="15">
         <v>1128.4689499999999</v>
@@ -8630,7 +8627,7 @@
     </row>
     <row r="79" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A79" s="16" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B79" s="2">
         <v>676103</v>
@@ -8639,7 +8636,7 @@
         <v>3893769</v>
       </c>
       <c r="D79" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G79" s="16" t="s">
         <v>72</v>
@@ -8711,7 +8708,7 @@
     </row>
     <row r="80" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A80" s="16" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B80" s="2">
         <v>675545</v>
@@ -8720,7 +8717,7 @@
         <v>3898078</v>
       </c>
       <c r="D80" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G80" s="16" t="s">
         <v>72</v>
@@ -8792,7 +8789,7 @@
     </row>
     <row r="81" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A81" s="16" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B81" s="2">
         <v>680279</v>
@@ -8801,7 +8798,7 @@
         <v>3897368</v>
       </c>
       <c r="D81" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G81" s="16" t="s">
         <v>72</v>
@@ -8873,7 +8870,7 @@
     </row>
     <row r="82" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A82" s="16" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B82" s="2">
         <v>679731</v>
@@ -8882,10 +8879,10 @@
         <v>3897647</v>
       </c>
       <c r="D82" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G82" s="16" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H82" s="15">
         <v>542.47939799999995</v>
@@ -8954,7 +8951,7 @@
     </row>
     <row r="83" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A83" s="16" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B83" s="2">
         <v>680735</v>
@@ -8970,7 +8967,7 @@
       </c>
       <c r="F83" s="16"/>
       <c r="G83" s="16" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H83" s="15">
         <v>721.05605700000001</v>
@@ -9039,7 +9036,7 @@
     </row>
     <row r="84" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A84" s="16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B84" s="2">
         <v>680553</v>
@@ -9048,10 +9045,10 @@
         <v>3894908</v>
       </c>
       <c r="D84" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G84" s="16" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H84" s="15">
         <v>779.57608400000004</v>
@@ -9120,7 +9117,7 @@
     </row>
     <row r="85" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A85" s="16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B85" s="2">
         <v>682891</v>
@@ -9129,7 +9126,7 @@
         <v>3892733</v>
       </c>
       <c r="D85" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G85" s="16" t="s">
         <v>72</v>
@@ -9201,7 +9198,7 @@
     </row>
     <row r="86" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A86" s="16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B86" s="2">
         <v>683049</v>
@@ -9284,7 +9281,7 @@
     </row>
     <row r="87" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A87" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B87" s="2">
         <v>686754</v>
@@ -9293,7 +9290,7 @@
         <v>3892178</v>
       </c>
       <c r="D87" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E87">
         <v>1</v>
@@ -9302,7 +9299,7 @@
         <v>1</v>
       </c>
       <c r="G87" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H87" s="15">
         <v>1360.517732</v>
@@ -9371,7 +9368,7 @@
     </row>
     <row r="88" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A88" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B88" s="2">
         <v>684015</v>
@@ -9454,7 +9451,7 @@
     </row>
     <row r="89" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A89" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B89" s="2">
         <v>683763</v>
@@ -9537,7 +9534,7 @@
     </row>
     <row r="90" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A90" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B90" s="2">
         <v>684872</v>
@@ -9620,7 +9617,7 @@
     </row>
     <row r="91" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A91" s="16" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B91" s="2">
         <v>685404</v>
@@ -9703,7 +9700,7 @@
     </row>
     <row r="92" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A92" s="16" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B92" s="2">
         <v>686676</v>
@@ -9712,12 +9709,12 @@
         <v>3895590</v>
       </c>
       <c r="D92" s="32" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E92" s="32"/>
       <c r="F92" s="32"/>
       <c r="G92" s="16" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H92" s="15">
         <v>178.908613</v>
@@ -9786,7 +9783,7 @@
     </row>
     <row r="93" spans="1:27" x14ac:dyDescent="0.45">
       <c r="A93" s="16" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B93" s="2">
         <v>689900</v>
@@ -9795,7 +9792,7 @@
         <v>3896051</v>
       </c>
       <c r="D93" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G93" s="16" t="s">
         <v>72</v>
@@ -9980,10 +9977,10 @@
         <v>190</v>
       </c>
       <c r="AB1" s="23" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AC1" s="5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.45">

--- a/data/Complete_dataset.xlsx
+++ b/data/Complete_dataset.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alvar\Repository\Roman-Chebba-agriculture\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pc\OneDrive\Documents\repos\Roman-Chebba-agriculture\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF6732F3-8DFF-4066-A081-E92AE62B92A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57CBA31E-138D-44D2-A923-F3859B266EC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Legend" sheetId="1" r:id="rId1"/>
@@ -18,19 +18,6 @@
     <sheet name="Other sites" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -1689,20 +1676,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="53.3984375" customWidth="1"/>
-    <col min="2" max="2" width="78.73046875" customWidth="1"/>
-    <col min="3" max="3" width="52.73046875" customWidth="1"/>
+    <col min="1" max="1" width="53.42578125" customWidth="1"/>
+    <col min="2" max="2" width="78.7109375" customWidth="1"/>
+    <col min="3" max="3" width="52.7109375" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="19.73046875" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="10" width="18" customWidth="1"/>
     <col min="11" max="11" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="34.15" x14ac:dyDescent="1.05">
+    <row r="1" spans="1:11" ht="34.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="20" t="s">
         <v>205</v>
       </c>
@@ -1710,7 +1697,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1718,7 +1705,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1726,7 +1713,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="30.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
         <v>10</v>
       </c>
@@ -1734,7 +1721,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
         <v>181</v>
       </c>
@@ -1742,7 +1729,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>182</v>
       </c>
@@ -1750,7 +1737,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>13</v>
       </c>
@@ -1758,12 +1745,12 @@
         <v>187</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="68.25" x14ac:dyDescent="1.05">
+    <row r="10" spans="1:11" ht="69" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="18" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>123</v>
       </c>
@@ -1795,7 +1782,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -1827,7 +1814,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>68</v>
       </c>
@@ -1859,7 +1846,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -1891,7 +1878,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -1923,7 +1910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -1943,7 +1930,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>66</v>
       </c>
@@ -1963,7 +1950,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>80</v>
       </c>
@@ -1983,7 +1970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -2003,7 +1990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
         <v>201</v>
       </c>
@@ -2017,7 +2004,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>202</v>
       </c>
@@ -2031,7 +2018,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
         <v>203</v>
       </c>
@@ -2045,12 +2032,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>162</v>
       </c>
@@ -2058,7 +2045,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>127</v>
       </c>
@@ -2066,7 +2053,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>128</v>
       </c>
@@ -2074,7 +2061,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>166</v>
       </c>
@@ -2082,7 +2069,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>168</v>
       </c>
@@ -2090,7 +2077,7 @@
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>15</v>
       </c>
@@ -2112,30 +2099,30 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AB93"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.3984375" style="16"/>
-    <col min="2" max="3" width="11.3984375" style="2"/>
-    <col min="4" max="6" width="43.73046875" customWidth="1"/>
-    <col min="7" max="7" width="35.1328125" customWidth="1"/>
-    <col min="8" max="9" width="11.3984375" style="15"/>
-    <col min="10" max="10" width="11.3984375" style="10"/>
-    <col min="13" max="13" width="11.3984375" style="11"/>
-    <col min="14" max="14" width="11.3984375" style="10"/>
-    <col min="16" max="16" width="14.86328125" customWidth="1"/>
-    <col min="17" max="17" width="11.3984375" style="11"/>
-    <col min="18" max="18" width="11.3984375" style="10"/>
+    <col min="1" max="1" width="11.42578125" style="16"/>
+    <col min="2" max="3" width="11.42578125" style="2"/>
+    <col min="4" max="6" width="43.7109375" customWidth="1"/>
+    <col min="7" max="7" width="35.140625" customWidth="1"/>
+    <col min="8" max="9" width="11.42578125" style="15"/>
+    <col min="10" max="10" width="11.42578125" style="10"/>
+    <col min="13" max="13" width="11.42578125" style="11"/>
+    <col min="14" max="14" width="11.42578125" style="10"/>
+    <col min="16" max="16" width="14.85546875" customWidth="1"/>
+    <col min="17" max="17" width="11.42578125" style="11"/>
+    <col min="18" max="18" width="11.42578125" style="10"/>
     <col min="20" max="20" width="18" customWidth="1"/>
-    <col min="21" max="21" width="20.265625" customWidth="1"/>
-    <col min="22" max="22" width="41.265625" customWidth="1"/>
+    <col min="21" max="21" width="20.28515625" customWidth="1"/>
+    <col min="22" max="22" width="41.28515625" customWidth="1"/>
     <col min="23" max="23" width="38" customWidth="1"/>
-    <col min="24" max="24" width="11.3984375" style="11"/>
-    <col min="25" max="25" width="18.1328125" style="10" customWidth="1"/>
+    <col min="24" max="24" width="11.42578125" style="11"/>
+    <col min="25" max="25" width="18.140625" style="10" customWidth="1"/>
     <col min="26" max="26" width="19" customWidth="1"/>
-    <col min="27" max="27" width="25.59765625" style="11" customWidth="1"/>
+    <col min="27" max="27" width="25.5703125" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="28.9" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:28" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
         <v>206</v>
       </c>
@@ -2221,7 +2208,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="26" t="s">
         <v>321</v>
       </c>
@@ -2304,7 +2291,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
         <v>264</v>
       </c>
@@ -2385,7 +2372,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
         <v>266</v>
       </c>
@@ -2469,7 +2456,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" s="26" t="s">
         <v>343</v>
       </c>
@@ -2553,7 +2540,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" s="26" t="s">
         <v>267</v>
       </c>
@@ -2636,7 +2623,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
         <v>295</v>
       </c>
@@ -2717,7 +2704,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" s="26" t="s">
         <v>320</v>
       </c>
@@ -2800,7 +2787,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" s="26" t="s">
         <v>318</v>
       </c>
@@ -2881,7 +2868,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" s="26" t="s">
         <v>297</v>
       </c>
@@ -2964,7 +2951,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" s="26" t="s">
         <v>316</v>
       </c>
@@ -3045,7 +3032,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" s="26" t="s">
         <v>273</v>
       </c>
@@ -3128,7 +3115,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A13" s="26" t="s">
         <v>271</v>
       </c>
@@ -3209,7 +3196,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A14" s="26" t="s">
         <v>260</v>
       </c>
@@ -3292,7 +3279,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A15" s="26" t="s">
         <v>259</v>
       </c>
@@ -3375,7 +3362,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16" s="26" t="s">
         <v>261</v>
       </c>
@@ -3458,7 +3445,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
         <v>262</v>
       </c>
@@ -3539,7 +3526,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" s="26" t="s">
         <v>269</v>
       </c>
@@ -3623,7 +3610,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" s="26" t="s">
         <v>275</v>
       </c>
@@ -3703,7 +3690,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" s="26" t="s">
         <v>277</v>
       </c>
@@ -3783,7 +3770,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" s="26" t="s">
         <v>285</v>
       </c>
@@ -3867,7 +3854,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A22" s="26" t="s">
         <v>287</v>
       </c>
@@ -3951,7 +3938,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23" s="26" t="s">
         <v>289</v>
       </c>
@@ -4032,7 +4019,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" s="26" t="s">
         <v>283</v>
       </c>
@@ -4113,7 +4100,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" s="26" t="s">
         <v>281</v>
       </c>
@@ -4194,7 +4181,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A26" s="26" t="s">
         <v>279</v>
       </c>
@@ -4276,7 +4263,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A27" s="26" t="s">
         <v>256</v>
       </c>
@@ -4358,7 +4345,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A28" s="26" t="s">
         <v>258</v>
       </c>
@@ -4440,7 +4427,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A29" s="26" t="s">
         <v>254</v>
       </c>
@@ -4526,7 +4513,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A30" s="26" t="s">
         <v>314</v>
       </c>
@@ -4609,7 +4596,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A31" s="26" t="s">
         <v>253</v>
       </c>
@@ -4623,7 +4610,7 @@
         <v>72</v>
       </c>
       <c r="E31" s="27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31" s="27"/>
       <c r="G31" s="16" t="s">
@@ -4690,7 +4677,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A32" s="26" t="s">
         <v>250</v>
       </c>
@@ -4771,7 +4758,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A33" s="26" t="s">
         <v>248</v>
       </c>
@@ -4854,7 +4841,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A34" s="26" t="s">
         <v>252</v>
       </c>
@@ -4935,7 +4922,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A35" s="26" t="s">
         <v>246</v>
       </c>
@@ -5018,7 +5005,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A36" s="26" t="s">
         <v>245</v>
       </c>
@@ -5101,7 +5088,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A37" s="26" t="s">
         <v>244</v>
       </c>
@@ -5184,7 +5171,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A38" s="26" t="s">
         <v>242</v>
       </c>
@@ -5269,7 +5256,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A39" s="26" t="s">
         <v>349</v>
       </c>
@@ -5356,7 +5343,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A40" s="26" t="s">
         <v>240</v>
       </c>
@@ -5437,7 +5424,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A41" s="26" t="s">
         <v>239</v>
       </c>
@@ -5520,7 +5507,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A42" s="26" t="s">
         <v>212</v>
       </c>
@@ -5604,7 +5591,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A43" s="26" t="s">
         <v>213</v>
       </c>
@@ -5687,7 +5674,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A44" s="26" t="s">
         <v>210</v>
       </c>
@@ -5770,7 +5757,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A45" s="26" t="s">
         <v>209</v>
       </c>
@@ -5853,7 +5840,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A46" s="26" t="s">
         <v>208</v>
       </c>
@@ -5936,7 +5923,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A47" s="26" t="s">
         <v>207</v>
       </c>
@@ -6019,7 +6006,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A48" s="26" t="s">
         <v>215</v>
       </c>
@@ -6104,7 +6091,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A49" s="26" t="s">
         <v>214</v>
       </c>
@@ -6187,7 +6174,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A50" s="26" t="s">
         <v>238</v>
       </c>
@@ -6270,7 +6257,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A51" s="26" t="s">
         <v>236</v>
       </c>
@@ -6353,7 +6340,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A52" s="26" t="s">
         <v>235</v>
       </c>
@@ -6440,7 +6427,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A53" s="26" t="s">
         <v>352</v>
       </c>
@@ -6527,7 +6514,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A54" s="26" t="s">
         <v>234</v>
       </c>
@@ -6612,7 +6599,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A55" s="26" t="s">
         <v>231</v>
       </c>
@@ -6699,7 +6686,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A56" s="26" t="s">
         <v>232</v>
       </c>
@@ -6782,7 +6769,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A57" s="26" t="s">
         <v>233</v>
       </c>
@@ -6865,7 +6852,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A58" s="26" t="s">
         <v>225</v>
       </c>
@@ -6946,7 +6933,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A59" s="26" t="s">
         <v>227</v>
       </c>
@@ -7033,7 +7020,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A60" s="26" t="s">
         <v>312</v>
       </c>
@@ -7046,10 +7033,10 @@
       <c r="D60" s="25" t="s">
         <v>313</v>
       </c>
-      <c r="E60" s="25"/>
-      <c r="F60" s="25">
+      <c r="E60" s="25">
         <v>1</v>
       </c>
+      <c r="F60" s="25"/>
       <c r="G60" t="s">
         <v>345</v>
       </c>
@@ -7118,7 +7105,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A61" s="26" t="s">
         <v>291</v>
       </c>
@@ -7199,7 +7186,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A62" s="26" t="s">
         <v>292</v>
       </c>
@@ -7282,7 +7269,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A63" s="26" t="s">
         <v>306</v>
       </c>
@@ -7365,7 +7352,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A64" s="26" t="s">
         <v>304</v>
       </c>
@@ -7448,7 +7435,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A65" s="26" t="s">
         <v>308</v>
       </c>
@@ -7532,7 +7519,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A66" s="26" t="s">
         <v>325</v>
       </c>
@@ -7613,7 +7600,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A67" s="26" t="s">
         <v>305</v>
       </c>
@@ -7696,7 +7683,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="68" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A68" s="26" t="s">
         <v>302</v>
       </c>
@@ -7779,7 +7766,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A69" s="26" t="s">
         <v>300</v>
       </c>
@@ -7862,7 +7849,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A70" s="26" t="s">
         <v>299</v>
       </c>
@@ -7949,7 +7936,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="71" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A71" s="26" t="s">
         <v>303</v>
       </c>
@@ -8032,7 +8019,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A72" s="26" t="s">
         <v>324</v>
       </c>
@@ -8117,7 +8104,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A73" s="26" t="s">
         <v>322</v>
       </c>
@@ -8204,7 +8191,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="74" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A74" s="26" t="s">
         <v>329</v>
       </c>
@@ -8287,7 +8274,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="75" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A75" s="26" t="s">
         <v>333</v>
       </c>
@@ -8370,7 +8357,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A76" s="26" t="s">
         <v>331</v>
       </c>
@@ -8457,7 +8444,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A77" s="26" t="s">
         <v>327</v>
       </c>
@@ -8538,7 +8525,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="78" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A78" s="16" t="s">
         <v>335</v>
       </c>
@@ -8625,7 +8612,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A79" s="16" t="s">
         <v>337</v>
       </c>
@@ -8706,7 +8693,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A80" s="16" t="s">
         <v>339</v>
       </c>
@@ -8787,7 +8774,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A81" s="16" t="s">
         <v>223</v>
       </c>
@@ -8868,7 +8855,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A82" s="16" t="s">
         <v>357</v>
       </c>
@@ -8949,7 +8936,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A83" s="16" t="s">
         <v>222</v>
       </c>
@@ -9034,7 +9021,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A84" s="16" t="s">
         <v>311</v>
       </c>
@@ -9115,7 +9102,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="85" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A85" s="16" t="s">
         <v>219</v>
       </c>
@@ -9196,7 +9183,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A86" s="16" t="s">
         <v>221</v>
       </c>
@@ -9279,7 +9266,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="87" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A87" s="16" t="s">
         <v>218</v>
       </c>
@@ -9366,7 +9353,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="88" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A88" s="16" t="s">
         <v>228</v>
       </c>
@@ -9449,7 +9436,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A89" s="16" t="s">
         <v>229</v>
       </c>
@@ -9532,7 +9519,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A90" s="16" t="s">
         <v>230</v>
       </c>
@@ -9615,7 +9602,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="91" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A91" s="16" t="s">
         <v>310</v>
       </c>
@@ -9698,7 +9685,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A92" s="16" t="s">
         <v>367</v>
       </c>
@@ -9781,7 +9768,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="93" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A93" s="16" t="s">
         <v>216</v>
       </c>
@@ -9874,27 +9861,27 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AE53"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="34.1328125" customWidth="1"/>
-    <col min="4" max="4" width="16.265625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="14.86328125" style="2" customWidth="1"/>
-    <col min="9" max="14" width="11.3984375" style="15"/>
-    <col min="15" max="15" width="11.3984375" style="10"/>
+    <col min="3" max="3" width="34.140625" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="2" customWidth="1"/>
+    <col min="9" max="14" width="11.42578125" style="15"/>
+    <col min="15" max="15" width="11.42578125" style="10"/>
     <col min="16" max="16" width="16" customWidth="1"/>
     <col min="17" max="17" width="18" customWidth="1"/>
     <col min="18" max="18" width="12" style="11" customWidth="1"/>
-    <col min="19" max="19" width="11.3984375" style="10"/>
+    <col min="19" max="19" width="11.42578125" style="10"/>
     <col min="21" max="21" width="20" customWidth="1"/>
     <col min="22" max="22" width="14" customWidth="1"/>
     <col min="23" max="23" width="26" customWidth="1"/>
     <col min="24" max="24" width="16" customWidth="1"/>
     <col min="25" max="25" width="12" style="11" customWidth="1"/>
-    <col min="26" max="26" width="29.3984375" style="10" customWidth="1"/>
+    <col min="26" max="26" width="29.42578125" style="10" customWidth="1"/>
     <col min="28" max="28" width="21" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="5" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:29" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -9983,7 +9970,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>7</v>
       </c>
@@ -10080,7 +10067,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>8</v>
       </c>
@@ -10177,7 +10164,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9</v>
       </c>
@@ -10274,7 +10261,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>10</v>
       </c>
@@ -10371,7 +10358,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>11</v>
       </c>
@@ -10468,7 +10455,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>12</v>
       </c>
@@ -10565,7 +10552,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>19</v>
       </c>
@@ -10662,7 +10649,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>20</v>
       </c>
@@ -10759,7 +10746,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>21</v>
       </c>
@@ -10856,7 +10843,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>22</v>
       </c>
@@ -10953,7 +10940,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>23</v>
       </c>
@@ -11050,7 +11037,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>24</v>
       </c>
@@ -11147,7 +11134,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>25</v>
       </c>
@@ -11244,7 +11231,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>26</v>
       </c>
@@ -11341,7 +11328,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>32</v>
       </c>
@@ -11438,7 +11425,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>33</v>
       </c>
@@ -11535,7 +11522,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="18" spans="1:31" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>34</v>
       </c>
@@ -11632,7 +11619,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="19" spans="1:31" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>35</v>
       </c>
@@ -11730,7 +11717,7 @@
       </c>
       <c r="AE19" s="13"/>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>36</v>
       </c>
@@ -11827,7 +11814,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>44</v>
       </c>
@@ -11924,7 +11911,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>45</v>
       </c>
@@ -12021,7 +12008,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>46</v>
       </c>
@@ -12118,7 +12105,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>47</v>
       </c>
@@ -12215,7 +12202,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>48</v>
       </c>
@@ -12312,7 +12299,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>49</v>
       </c>
@@ -12409,7 +12396,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>50</v>
       </c>
@@ -12506,7 +12493,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>51</v>
       </c>
@@ -12603,7 +12590,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="29" spans="1:31" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:31" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="35">
         <v>0</v>
       </c>
@@ -12700,7 +12687,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="30" spans="1:31" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:31" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="35">
         <v>1</v>
       </c>
@@ -12797,7 +12784,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:31" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:31" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="35">
         <v>2</v>
       </c>
@@ -12894,7 +12881,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:31" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:31" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="35">
         <v>3</v>
       </c>
@@ -12991,7 +12978,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="35">
         <v>4</v>
       </c>
@@ -13088,7 +13075,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="34" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="35">
         <v>5</v>
       </c>
@@ -13185,7 +13172,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="35">
         <v>6</v>
       </c>
@@ -13282,7 +13269,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="36" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="35">
         <v>13</v>
       </c>
@@ -13379,7 +13366,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="37" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="35">
         <v>14</v>
       </c>
@@ -13476,7 +13463,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="38" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="35">
         <v>15</v>
       </c>
@@ -13573,7 +13560,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="39" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="35">
         <v>16</v>
       </c>
@@ -13670,7 +13657,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="40" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="35">
         <v>17</v>
       </c>
@@ -13767,7 +13754,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="41" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="35">
         <v>18</v>
       </c>
@@ -13864,7 +13851,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="42" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="35">
         <v>27</v>
       </c>
@@ -13961,7 +13948,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="43" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="35">
         <v>28</v>
       </c>
@@ -14058,7 +14045,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="44" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="35">
         <v>29</v>
       </c>
@@ -14155,7 +14142,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="45" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="35">
         <v>30</v>
       </c>
@@ -14252,7 +14239,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="46" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="35">
         <v>31</v>
       </c>
@@ -14349,7 +14336,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="47" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="35">
         <v>37</v>
       </c>
@@ -14446,7 +14433,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="48" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="35">
         <v>38</v>
       </c>
@@ -14543,7 +14530,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="49" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="35">
         <v>39</v>
       </c>
@@ -14640,7 +14627,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="50" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="35">
         <v>40</v>
       </c>
@@ -14737,7 +14724,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="51" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="35">
         <v>41</v>
       </c>
@@ -14834,7 +14821,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="52" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="35">
         <v>42</v>
       </c>
@@ -14931,7 +14918,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="53" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:29" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="35">
         <v>43</v>
       </c>
